--- a/output/pdf_financials_xlsx/CFP.xlsx
+++ b/output/pdf_financials_xlsx/CFP.xlsx
@@ -7300,10 +7300,10 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -7315,13 +7315,13 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M112" s="1" t="inlineStr">
         <is>
@@ -43152,7 +43152,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -50312,7 +50316,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
